--- a/sources/cc_sectors.xlsx
+++ b/sources/cc_sectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamw\Nextcloud\Projects\UNEP-Gap-Report-2025-Chapter-2\sources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamw\Nextcloud\Projects\UNEP-Gap-Report-2026-Chapter-2\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,13 +13,14 @@
   </bookViews>
   <sheets>
     <sheet name="sectors" sheetId="1" r:id="rId1"/>
+    <sheet name="depreciated" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="151">
   <si>
     <t>code</t>
   </si>
@@ -454,6 +455,24 @@
   </si>
   <si>
     <t>Waste</t>
+  </si>
+  <si>
+    <t>1.A.3.b</t>
+  </si>
+  <si>
+    <t>Road Transportation</t>
+  </si>
+  <si>
+    <t>4.E</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Other waste</t>
+  </si>
+  <si>
+    <t>4E</t>
   </si>
 </sst>
 </file>
@@ -797,6 +816,1370 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="6" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J11" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J21" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" t="s">
+        <v>123</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+      <c r="G23" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J24" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J31" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J32" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J33" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J35" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J36" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J38" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" t="s">
+        <v>96</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" t="s">
+        <v>149</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" t="s">
+        <v>125</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="2">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2122,7 +3505,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>